--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:39:27+00:00</t>
+    <t>2026-06-12T12:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:41:39+00:00</t>
+    <t>2026-06-12T12:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:48:36+00:00</t>
+    <t>2026-06-12T12:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:50:08+00:00</t>
+    <t>2026-06-12T12:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:51:11+00:00</t>
+    <t>2026-06-12T12:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:53:38+00:00</t>
+    <t>2026-06-12T12:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:54:18+00:00</t>
+    <t>2026-06-12T12:56:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:56:21+00:00</t>
+    <t>2026-06-12T12:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:57:59+00:00</t>
+    <t>2026-06-12T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:09:22+00:00</t>
+    <t>2026-06-12T13:12:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:12:41+00:00</t>
+    <t>2026-06-12T13:14:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:14:22+00:00</t>
+    <t>2026-06-12T13:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/initial-ig-spec/ig/all-profiles.xlsx
+++ b/feat/initial-ig-spec/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:14:17+00:00</t>
+    <t>2026-06-18T12:46:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
